--- a/metadata/Data 2023 For Syl Segmentation_3.xlsx
+++ b/metadata/Data 2023 For Syl Segmentation_3.xlsx
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F221" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F224" t="n">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F237" t="n">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F238" t="n">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F322" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F348" t="n">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F351" t="n">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F352" t="n">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F357" t="n">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F358" t="n">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F359" t="n">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F360" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F362" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F363" t="n">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F364" t="n">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F365" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F366" t="n">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F367" t="n">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F368" t="n">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F383" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F384" t="n">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F385" t="n">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F386" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F387" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F388" t="n">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F389" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F390" t="n">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F391" t="n">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F392" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F393" t="n">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F399" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F400" t="n">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F401" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F402" t="n">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F403" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F404" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F405" t="n">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F406" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F407" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F418" t="n">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F419" t="n">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F420" t="n">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F421" t="n">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F439" t="n">
@@ -17137,7 +17137,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F440" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F441" t="n">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F442" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F443" t="n">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F444" t="n">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F445" t="n">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -17669,7 +17669,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -17821,7 +17821,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F459" t="n">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F460" t="n">
@@ -17935,7 +17935,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F461" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F462" t="n">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F463" t="n">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F464" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F465" t="n">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F466" t="n">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F467" t="n">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F468" t="n">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F469" t="n">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F470" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F471" t="n">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -18695,7 +18695,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F482" t="n">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F483" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F484" t="n">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F485" t="n">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F486" t="n">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F487" t="n">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F488" t="n">
@@ -18999,7 +18999,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F489" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F492" t="n">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F493" t="n">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F494" t="n">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F495" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F496" t="n">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -19531,7 +19531,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -19645,7 +19645,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F507" t="n">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F508" t="n">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F509" t="n">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F510" t="n">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F511" t="n">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F512" t="n">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F513" t="n">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F514" t="n">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F515" t="n">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F516" t="n">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F517" t="n">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F518" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F519" t="n">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F520" t="n">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F522" t="n">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F523" t="n">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F524" t="n">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F525" t="n">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F526" t="n">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F527" t="n">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F528" t="n">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F529" t="n">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F530" t="n">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F531" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F532" t="n">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F533" t="n">
@@ -20709,7 +20709,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F534" t="n">
@@ -20747,7 +20747,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F535" t="n">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F536" t="n">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F537" t="n">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F539" t="n">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F540" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -21013,7 +21013,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F542" t="n">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F543" t="n">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F544" t="n">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F545" t="n">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F549" t="n">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F550" t="n">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F555" t="n">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F556" t="n">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F557" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F558" t="n">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F559" t="n">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F560" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F561" t="n">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F562" t="n">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F563" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F564" t="n">
@@ -21887,7 +21887,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F565" t="n">
@@ -21925,7 +21925,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F566" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F567" t="n">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F568" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F569" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F570" t="n">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F571" t="n">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F572" t="n">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F573" t="n">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F575" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F580" t="n">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F583" t="n">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F585" t="n">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F586" t="n">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F595" t="n">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F596" t="n">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F607" t="n">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F608" t="n">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F609" t="n">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F610" t="n">
@@ -23635,7 +23635,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F611" t="n">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F612" t="n">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F613" t="n">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F614" t="n">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F615" t="n">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F616" t="n">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F617" t="n">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F618" t="n">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F619" t="n">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F621" t="n">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F622" t="n">
@@ -24091,7 +24091,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F623" t="n">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F624" t="n">
@@ -24167,7 +24167,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F625" t="n">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F626" t="n">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F627" t="n">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F628" t="n">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F629" t="n">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F632" t="n">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F636" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F637" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F638" t="n">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -24737,7 +24737,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -24851,7 +24851,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -24889,7 +24889,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -24965,7 +24965,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F648" t="n">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F649" t="n">
@@ -25117,7 +25117,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F650" t="n">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F651" t="n">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F652" t="n">
@@ -25231,7 +25231,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F654" t="n">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F655" t="n">
@@ -25345,7 +25345,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F656" t="n">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F657" t="n">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F658" t="n">
@@ -25459,7 +25459,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -25535,7 +25535,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -25649,7 +25649,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -25877,7 +25877,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F670" t="n">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F672" t="n">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -26105,7 +26105,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -26143,7 +26143,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F679" t="n">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F680" t="n">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -26371,7 +26371,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -26599,7 +26599,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F689" t="n">
@@ -26637,7 +26637,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -26675,7 +26675,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F691" t="n">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F692" t="n">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F693" t="n">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F694" t="n">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F695" t="n">
@@ -26865,7 +26865,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F696" t="n">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F697" t="n">
@@ -26941,7 +26941,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F698" t="n">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F699" t="n">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F700" t="n">
@@ -27055,7 +27055,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F701" t="n">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F702" t="n">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F703" t="n">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F704" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F705" t="n">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F706" t="n">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F707" t="n">
@@ -27321,7 +27321,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F708" t="n">
@@ -27359,7 +27359,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F709" t="n">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F710" t="n">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F711" t="n">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F712" t="n">
